--- a/ucchshiksha.xlsx
+++ b/ucchshiksha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\demo\project2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B741D870-159B-4DA7-878B-69D3A3FE9C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D730BE8-BB13-4A0D-A247-4039461C9991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t xml:space="preserve">ssdf </t>
   </si>
@@ -46,6 +46,66 @@
   </si>
   <si>
     <t>e</t>
+  </si>
+  <si>
+    <t>ti was jlkjiow jkj</t>
+  </si>
+  <si>
+    <t>ijhjhoi</t>
+  </si>
+  <si>
+    <t>kljlkjoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ijdfoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> joieroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jijikriuj</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> joijsfoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> hfoihoij</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> iehfoij</t>
+  </si>
+  <si>
+    <t>k ufioi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> oihoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fihoi</t>
+  </si>
+  <si>
+    <t>I fiwio</t>
+  </si>
+  <si>
+    <t>u ik</t>
+  </si>
+  <si>
+    <t>oi oi oioi1i</t>
+  </si>
+  <si>
+    <t>joi ijhoirh</t>
+  </si>
+  <si>
+    <t>oi h iwfoih</t>
+  </si>
+  <si>
+    <t>oihoi aihfoi</t>
+  </si>
+  <si>
+    <t>oihoi hoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jh </t>
   </si>
 </sst>
 </file>
@@ -363,50 +423,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="G6:G14"/>
+  <dimension ref="G6:AB14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>15</v>
+      </c>
+      <c r="R13" t="s">
+        <v>16</v>
+      </c>
+      <c r="S13" t="s">
+        <v>17</v>
+      </c>
+      <c r="T13" t="s">
+        <v>18</v>
+      </c>
+      <c r="U13" t="s">
+        <v>19</v>
+      </c>
+      <c r="V13" t="s">
+        <v>20</v>
+      </c>
+      <c r="W13" t="s">
+        <v>21</v>
+      </c>
+      <c r="X13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="7:28" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
         <v>6</v>
       </c>
